--- a/data/ams_weekly_data/Nexlev/ads_report_week19.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week19.xlsx
@@ -8351,7 +8351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7567.666666666667</v>
+        <v>7568</v>
       </c>
       <c r="E5" t="n">
         <v>19</v>
@@ -8546,7 +8546,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7567.666666666667</v>
+        <v>7568</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7567.666666666667</v>
+        <v>7568</v>
       </c>
       <c r="E7" t="n">
         <v>19</v>
@@ -8615,7 +8615,7 @@
         <v>1176</v>
       </c>
       <c r="E8" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="F8" t="n">
         <v>307.52</v>
@@ -8648,7 +8648,7 @@
         <v>1176</v>
       </c>
       <c r="E9" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
         <v>307.52</v>
@@ -8740,23 +8740,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2519</v>
+        <v>1184</v>
       </c>
       <c r="E12" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="F12" t="n">
-        <v>1714.23</v>
+        <v>805.6991190942622</v>
       </c>
       <c r="G12" t="n">
-        <v>5227.120000000001</v>
+        <v>2456.78</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -8768,25 +8768,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_ST-01_B0DVC7VJP1</t>
+          <t>Nex_HnK_SBV_KT_MR-02_B0DCK7ZH5P_BCG_Phrase &amp; Exact - Reel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16136</v>
+        <v>1335</v>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>3018.02</v>
+        <v>908.5308809057377</v>
       </c>
       <c r="G13" t="n">
-        <v>5012.71</v>
+        <v>2770.34</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -8801,28 +8801,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nex_HnK_SBV_KT_ST-01_B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>35345</v>
+        <v>16136</v>
       </c>
       <c r="E14" t="n">
-        <v>45.33333333333334</v>
+        <v>143</v>
       </c>
       <c r="F14" t="n">
-        <v>810.61</v>
+        <v>3018.02</v>
       </c>
       <c r="G14" t="n">
-        <v>1103.816666666667</v>
+        <v>5012.71</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8839,23 +8839,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>35345</v>
+        <v>56362</v>
       </c>
       <c r="E15" t="n">
-        <v>45.33333333333334</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>810.61</v>
+        <v>1292.616289269051</v>
       </c>
       <c r="G15" t="n">
-        <v>1103.816666666667</v>
+        <v>1760.17</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8872,23 +8872,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>35345</v>
+        <v>49673</v>
       </c>
       <c r="E16" t="n">
-        <v>45.33333333333334</v>
+        <v>64</v>
       </c>
       <c r="F16" t="n">
-        <v>810.61</v>
+        <v>1139.213710730949</v>
       </c>
       <c r="G16" t="n">
-        <v>1103.816666666667</v>
+        <v>1551.28</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8938,23 +8938,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11195.66666666667</v>
+        <v>33587</v>
       </c>
       <c r="E18" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>486.1633333333334</v>
+        <v>1458.49</v>
       </c>
       <c r="G18" t="n">
-        <v>847.1733333333333</v>
+        <v>2541.52</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -8966,28 +8966,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_VC-01/VC-02/VC-05_BCG_Phrase &amp; Exact</t>
+          <t>Nex_Hnk_SBV_KT_ST-01_B0DVC7VJP1_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11195.66666666667</v>
+        <v>1056</v>
       </c>
       <c r="E19" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>486.1633333333334</v>
+        <v>418.72</v>
       </c>
       <c r="G19" t="n">
-        <v>847.1733333333333</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -8999,28 +8999,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_VC-01/VC-02/VC-05_BCG_Phrase &amp; Exact</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11195.66666666667</v>
+        <v>14577</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="F20" t="n">
-        <v>486.1633333333334</v>
+        <v>6333.638115330996</v>
       </c>
       <c r="G20" t="n">
-        <v>847.1733333333333</v>
+        <v>27887.16338710505</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3333333333333333</v>
+        <v>10</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9032,28 +9032,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SBV_KT_ST-01_B0DVC7VJP1_Phrase &amp; Exact</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1056</v>
+        <v>3925</v>
       </c>
       <c r="E21" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>418.72</v>
+        <v>1667.471355249351</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>6744.542833904763</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9070,23 +9070,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13836</v>
+        <v>7072</v>
       </c>
       <c r="E22" t="n">
-        <v>187.3333333333333</v>
+        <v>91</v>
       </c>
       <c r="F22" t="n">
-        <v>5957.419999999999</v>
+        <v>3004.153283985453</v>
       </c>
       <c r="G22" t="n">
-        <v>25376.56</v>
+        <v>12151.11758272193</v>
       </c>
       <c r="H22" t="n">
-        <v>9.333333333333334</v>
+        <v>5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9103,23 +9103,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13836</v>
+        <v>15934</v>
       </c>
       <c r="E23" t="n">
-        <v>187.3333333333333</v>
+        <v>216</v>
       </c>
       <c r="F23" t="n">
-        <v>5957.419999999999</v>
+        <v>6866.9972454342</v>
       </c>
       <c r="G23" t="n">
-        <v>25376.56</v>
+        <v>29346.85619626826</v>
       </c>
       <c r="H23" t="n">
-        <v>9.333333333333334</v>
+        <v>11</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9131,28 +9131,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13836</v>
+        <v>15047</v>
       </c>
       <c r="E24" t="n">
-        <v>187.3333333333333</v>
+        <v>561</v>
       </c>
       <c r="F24" t="n">
-        <v>5957.419999999999</v>
+        <v>6018.7</v>
       </c>
       <c r="G24" t="n">
-        <v>25376.56</v>
+        <v>29035.47</v>
       </c>
       <c r="H24" t="n">
-        <v>9.333333333333334</v>
+        <v>11</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9173,19 +9173,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7523.5</v>
+        <v>78021</v>
       </c>
       <c r="E25" t="n">
-        <v>280.5</v>
+        <v>257</v>
       </c>
       <c r="F25" t="n">
-        <v>3009.35</v>
+        <v>4921.01</v>
       </c>
       <c r="G25" t="n">
-        <v>14517.735</v>
+        <v>5331.43</v>
       </c>
       <c r="H25" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9197,28 +9197,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7523.5</v>
+        <v>21342</v>
       </c>
       <c r="E26" t="n">
-        <v>280.5</v>
+        <v>141</v>
       </c>
       <c r="F26" t="n">
-        <v>3009.35</v>
+        <v>1917.779144706114</v>
       </c>
       <c r="G26" t="n">
-        <v>14517.735</v>
+        <v>5348.636606318283</v>
       </c>
       <c r="H26" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -9230,28 +9230,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26007</v>
+        <v>11564</v>
       </c>
       <c r="E27" t="n">
-        <v>85.66666666666667</v>
+        <v>77</v>
       </c>
       <c r="F27" t="n">
-        <v>1640.336666666667</v>
+        <v>1039.110855293885</v>
       </c>
       <c r="G27" t="n">
-        <v>1777.143333333333</v>
+        <v>2898.053393681717</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6666666666666666</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9263,28 +9263,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26007</v>
+        <v>12171</v>
       </c>
       <c r="E28" t="n">
-        <v>85.66666666666667</v>
+        <v>304</v>
       </c>
       <c r="F28" t="n">
-        <v>1640.336666666667</v>
+        <v>3368.299979827576</v>
       </c>
       <c r="G28" t="n">
-        <v>1777.143333333333</v>
+        <v>12685.69023491446</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6666666666666666</v>
+        <v>7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9296,28 +9296,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>26007</v>
+        <v>1725</v>
       </c>
       <c r="E29" t="n">
-        <v>85.66666666666667</v>
+        <v>43</v>
       </c>
       <c r="F29" t="n">
-        <v>1640.336666666667</v>
+        <v>477.4600201724243</v>
       </c>
       <c r="G29" t="n">
-        <v>1777.143333333333</v>
+        <v>1798.209765085543</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9329,28 +9329,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10968.66666666667</v>
+        <v>26685</v>
       </c>
       <c r="E30" t="n">
-        <v>72.66666666666667</v>
+        <v>507</v>
       </c>
       <c r="F30" t="n">
-        <v>985.63</v>
+        <v>8594.67232349918</v>
       </c>
       <c r="G30" t="n">
-        <v>2748.896666666667</v>
+        <v>40378.86358779911</v>
       </c>
       <c r="H30" t="n">
-        <v>2.333333333333333</v>
+        <v>12</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9362,28 +9362,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10968.66666666667</v>
+        <v>3832</v>
       </c>
       <c r="E31" t="n">
-        <v>72.66666666666667</v>
+        <v>73</v>
       </c>
       <c r="F31" t="n">
-        <v>985.63</v>
+        <v>1234.277553741553</v>
       </c>
       <c r="G31" t="n">
-        <v>2748.896666666667</v>
+        <v>5798.792914506547</v>
       </c>
       <c r="H31" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9395,28 +9395,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10968.66666666667</v>
+        <v>3096</v>
       </c>
       <c r="E32" t="n">
-        <v>72.66666666666667</v>
+        <v>82</v>
       </c>
       <c r="F32" t="n">
-        <v>985.63</v>
+        <v>752.4101227592664</v>
       </c>
       <c r="G32" t="n">
-        <v>2748.896666666667</v>
+        <v>14172.17349769434</v>
       </c>
       <c r="H32" t="n">
-        <v>2.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9428,28 +9428,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6948</v>
+        <v>1728</v>
       </c>
       <c r="E33" t="n">
-        <v>173.5</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n">
-        <v>1922.88</v>
+        <v>415.915</v>
       </c>
       <c r="G33" t="n">
-        <v>7241.95</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -9461,28 +9461,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6948</v>
+        <v>1728</v>
       </c>
       <c r="E34" t="n">
-        <v>173.5</v>
+        <v>50</v>
       </c>
       <c r="F34" t="n">
-        <v>1922.88</v>
+        <v>415.915</v>
       </c>
       <c r="G34" t="n">
-        <v>7241.95</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -9494,28 +9494,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>33613</v>
+        <v>22020</v>
       </c>
       <c r="E35" t="n">
-        <v>662</v>
+        <v>475</v>
       </c>
       <c r="F35" t="n">
-        <v>10581.36</v>
+        <v>11396.49</v>
       </c>
       <c r="G35" t="n">
-        <v>60349.83</v>
+        <v>30832.19</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9527,28 +9527,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1728.5</v>
+        <v>9642</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="F36" t="n">
-        <v>415.915</v>
+        <v>986.9403151679553</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>6871.915219802373</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9560,28 +9560,28 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1728.5</v>
+        <v>8798</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F37" t="n">
-        <v>415.915</v>
+        <v>900.5614144715902</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>6270.472079581545</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9602,19 +9602,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>22020</v>
+        <v>13738</v>
       </c>
       <c r="E38" t="n">
-        <v>475</v>
+        <v>111</v>
       </c>
       <c r="F38" t="n">
-        <v>11396.49</v>
+        <v>1406.248270360455</v>
       </c>
       <c r="G38" t="n">
-        <v>30832.19</v>
+        <v>9791.492700616085</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -9626,162 +9626,30 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10726</v>
+        <v>80300</v>
       </c>
       <c r="E39" t="n">
-        <v>86.33333333333333</v>
+        <v>239</v>
       </c>
       <c r="F39" t="n">
-        <v>1097.916666666667</v>
+        <v>2319.36</v>
       </c>
       <c r="G39" t="n">
-        <v>7644.626666666667</v>
+        <v>4824.58</v>
       </c>
       <c r="H39" t="n">
-        <v>2.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10726</v>
-      </c>
-      <c r="E40" t="n">
-        <v>86.33333333333333</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1097.916666666667</v>
-      </c>
-      <c r="G40" t="n">
-        <v>7644.626666666667</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10726</v>
-      </c>
-      <c r="E41" t="n">
-        <v>86.33333333333333</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1097.916666666667</v>
-      </c>
-      <c r="G41" t="n">
-        <v>7644.626666666667</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>40150</v>
-      </c>
-      <c r="E42" t="n">
-        <v>119.5</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1159.68</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2412.29</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>40150</v>
-      </c>
-      <c r="E43" t="n">
-        <v>119.5</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1159.68</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2412.29</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week19.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week19.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
